--- a/workspace/framework_paper/fp/gradient_fp_eval_times.xlsx
+++ b/workspace/framework_paper/fp/gradient_fp_eval_times.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,41 +442,25 @@
           <t>bf</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>eqs</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>eqf</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0006078940012957901</v>
+        <v>0.0009158358187414706</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0005104480008594692</v>
+        <v>0.0008042809180915356</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007041120040230453</v>
+        <v>0.001081435803789645</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002344139968045056</v>
+        <v>0.0003596790600568056</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1120557023584843</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.0002340740012004972</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0002142180013470352</v>
+        <v>1.943361297845841</v>
       </c>
     </row>
     <row r="3">
@@ -484,25 +468,19 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0005849220021627844</v>
+        <v>0.0009291251259855926</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004807500005699694</v>
+        <v>0.0007754291972378269</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000686172004789114</v>
+        <v>0.0009994558745529502</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002255420049186796</v>
+        <v>0.0003398466389626264</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1003888495266438</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.0002270300011150539</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.0002084280038252473</v>
+        <v>1.965778627842665</v>
       </c>
     </row>
     <row r="4">
@@ -510,25 +488,19 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0005948999978136272</v>
+        <v>0.0008981659158598631</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0005382720031775534</v>
+        <v>0.0007763533398974687</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007642460009083152</v>
+        <v>0.001094322538701817</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002500640030484647</v>
+        <v>0.0003848207788541913</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09635469391942024</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.00021468999912031</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0001955180056393146</v>
+        <v>2.089400047510862</v>
       </c>
     </row>
     <row r="5">
@@ -536,25 +508,19 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0006268540001474321</v>
+        <v>0.000863934961380437</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0005434800020884722</v>
+        <v>0.0007619491836521775</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0007674720056820661</v>
+        <v>0.001069838341791183</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002653360064141452</v>
+        <v>0.0003553766960976646</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09080772012472153</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.0002154700004030019</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0001980199979152531</v>
+        <v>2.186939741373062</v>
       </c>
     </row>
     <row r="6">
@@ -562,25 +528,19 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0006185940001159906</v>
+        <v>0.0009975107776699589</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000519910000730306</v>
+        <v>0.0008940798771800473</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0007514299941249192</v>
+        <v>0.001211873326683417</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0002543459937442094</v>
+        <v>0.0003793699608650058</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08861884206533432</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.0002254159946460277</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0002022980025503785</v>
+        <v>2.204335668534041</v>
       </c>
     </row>
     <row r="7">
@@ -588,25 +548,19 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0006877440004609526</v>
+        <v>0.001089407600229606</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0005902999942190945</v>
+        <v>0.0009944108879426494</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008404820098076016</v>
+        <v>0.001346208425238729</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002750200079753995</v>
+        <v>0.0004412657406646758</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08309098400175571</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.000230164002859965</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0002042479964438826</v>
+        <v>2.353564262986183</v>
       </c>
     </row>
     <row r="8">
@@ -614,25 +568,19 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0007201239990536123</v>
+        <v>0.00107317159359809</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000625903996406123</v>
+        <v>0.0009506042039720341</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0008711859991308302</v>
+        <v>0.00132600081153214</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003062899922952056</v>
+        <v>0.0004505083191907033</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08172576017677784</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.0002394699992146343</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.0002201459999196231</v>
+        <v>2.388543365001679</v>
       </c>
     </row>
     <row r="9">
@@ -640,25 +588,19 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.00170496002654545</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005467671934748068</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001031240001320839</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0003127839951775968</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07724966794252396</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.0002177080023102462</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0002183280035387725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -666,25 +608,19 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.00131898999447003</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003407344078877941</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0009443200018722564</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0002852280007209629</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07669063344597817</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.0002315239969175309</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.0002109979989472777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -692,25 +628,19 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.002141114000696689</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00855716589372605</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001064438002649695</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0003045140020549297</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07546308405697345</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.0002452460001222789</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0002428500005044043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -718,25 +648,19 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.008525795838795602</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.03205162703525275</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.004567636022111401</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000326951997121796</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.07498907186090946</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.0002335659961681813</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.0002121379994787276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -744,25 +668,19 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.009423471967456862</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04618698047706857</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00686724791652523</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0003362999996170402</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.07280523635447025</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.0002258780016563833</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.000209371994715184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -770,25 +688,19 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0121856483456213</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.09479363597580232</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.009371754138264805</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0003134559991303831</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0697693357616663</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.0002250459988135844</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.0002044919994659722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -796,25 +708,19 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0.02785166564863175</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1242883774172515</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01823440594016574</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.000299330004490912</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0704224244505167</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.000215781998122111</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.0002012979949358851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -822,25 +728,19 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0554284535034094</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1701282319880556</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02155059397104196</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0003067639947403222</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.07204400233924389</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.0002391040022484958</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.0002169759979005903</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -848,25 +748,19 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0.068606415692484</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2605399218283128</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02520573184010573</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0002909340045880526</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0717029695212841</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.0002276860002893955</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.0002074939990416169</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -874,25 +768,19 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0.08657643202110193</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3291152002685703</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.03920828574686311</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0002777219994459301</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.07130182050168514</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.0001978479989338666</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.0002072099945507944</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -900,25 +788,19 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1393165824282915</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5549863688810729</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.04983227002667263</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0002884680056013167</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07200816787779331</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.00019572600023821</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.0002001859981101006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -926,25 +808,19 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0.2239494167640805</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9387931512191426</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.09033007019781508</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0002403239964041859</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07631304785609246</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.0001828880026005208</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.0001766519970260561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -952,25 +828,19 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0.3615253525984008</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1.393941343099577</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1094491291488521</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000270878003211692</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.07988286197185517</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.0001714219967834651</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.0001742239994928241</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/workspace/framework_paper/fp/gradient_fp_eval_times.xlsx
+++ b/workspace/framework_paper/fp/gradient_fp_eval_times.xlsx
@@ -448,19 +448,19 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0009158358187414706</v>
+        <v>0.0007893919968046248</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008042809180915356</v>
+        <v>0.0006229959963820875</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001081435803789645</v>
+        <v>0.0008899160078726709</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003596790600568056</v>
+        <v>0.000296412002062425</v>
       </c>
       <c r="F2" t="n">
-        <v>1.943361297845841</v>
+        <v>2.193019996732473</v>
       </c>
     </row>
     <row r="3">
@@ -468,19 +468,19 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0009291251259855926</v>
+        <v>0.0008400840067770332</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0007754291972378269</v>
+        <v>0.0006830139993689954</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009994558745529502</v>
+        <v>0.0009924079955089837</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003398466389626264</v>
+        <v>0.000331159996567294</v>
       </c>
       <c r="F3" t="n">
-        <v>1.965778627842665</v>
+        <v>2.275343377739191</v>
       </c>
     </row>
     <row r="4">
@@ -488,19 +488,19 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0008981659158598631</v>
+        <v>0.0007881999947130681</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007763533398974687</v>
+        <v>0.0006662339984904974</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001094322538701817</v>
+        <v>0.0009793319995515049</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003848207788541913</v>
+        <v>0.0003401659987866879</v>
       </c>
       <c r="F4" t="n">
-        <v>2.089400047510862</v>
+        <v>2.391024669408798</v>
       </c>
     </row>
     <row r="5">
@@ -508,19 +508,19 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.000863934961380437</v>
+        <v>0.0008843100012745709</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0007619491836521775</v>
+        <v>0.0007104880036786199</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001069838341791183</v>
+        <v>0.001003630006453022</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0003553766960976646</v>
+        <v>0.000338423999492079</v>
       </c>
       <c r="F5" t="n">
-        <v>2.186939741373062</v>
+        <v>2.479341176003218</v>
       </c>
     </row>
     <row r="6">
@@ -528,19 +528,19 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0009975107776699589</v>
+        <v>0.0008535460056737066</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008940798771800473</v>
+        <v>0.0006986679986584932</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001211873326683417</v>
+        <v>0.0009932979987934232</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003793699608650058</v>
+        <v>0.0003352339996490627</v>
       </c>
       <c r="F6" t="n">
-        <v>2.204335668534041</v>
+        <v>2.468851282894611</v>
       </c>
     </row>
     <row r="7">
@@ -548,19 +548,19 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.001089407600229606</v>
+        <v>0.0008797379978932441</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0009944108879426494</v>
+        <v>0.0007441119966097176</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001346208425238729</v>
+        <v>0.00106908198678866</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0004412657406646758</v>
+        <v>0.0003569219983182848</v>
       </c>
       <c r="F7" t="n">
-        <v>2.353564262986183</v>
+        <v>2.635712263733148</v>
       </c>
     </row>
     <row r="8">
@@ -568,19 +568,19 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.00107317159359809</v>
+        <v>0.0009212179912719876</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009506042039720341</v>
+        <v>0.0007944499934092165</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00132600081153214</v>
+        <v>0.00110066200606525</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0004505083191907033</v>
+        <v>0.0003760340018197894</v>
       </c>
       <c r="F8" t="n">
-        <v>2.388543365001679</v>
+        <v>2.701351160407066</v>
       </c>
     </row>
     <row r="9">
@@ -588,19 +588,19 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.0009319500008132309</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.0007891400007065386</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.001144340011524036</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.0003807940008118749</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2.782697332799435</v>
       </c>
     </row>
     <row r="10">
@@ -608,19 +608,19 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.0009932599868625403</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.000824383997824043</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.001171486008679494</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.0004017680045217275</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2.90157602712512</v>
       </c>
     </row>
     <row r="11">
@@ -628,19 +628,19 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.001332722010556608</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.001515297988662496</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.003017974039539695</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.0003867339994758367</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2.968516656160355</v>
       </c>
     </row>
     <row r="12">
@@ -648,19 +648,19 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.001969517994439229</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.00292254195548594</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.003310091966995969</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.0004288360057398677</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>3.201081767827272</v>
       </c>
     </row>
     <row r="13">
@@ -668,19 +668,19 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.003633842011913657</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.006339989937841893</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.0027825000253506</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.0004011200042441487</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3.409722273796797</v>
       </c>
     </row>
     <row r="14">
@@ -688,19 +688,19 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.005230469992384314</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.009772487917216495</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.008139245908241719</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.0004070640017744154</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>3.697639360427857</v>
       </c>
     </row>
     <row r="15">
@@ -708,19 +708,19 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.009944973828969523</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.03879417071584612</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.01291843803133816</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.0004055099980905652</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>4.261405312269926</v>
       </c>
     </row>
     <row r="16">
@@ -728,19 +728,19 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.02976611061953008</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.09482922577881255</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.01550610190955922</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.0003790280048269779</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>4.747784471660853</v>
       </c>
     </row>
     <row r="17">
@@ -748,19 +748,19 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.06512665909598582</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.211364009026438</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.02088046004297212</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.0004187360010109842</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>5.363029298633337</v>
       </c>
     </row>
     <row r="18">
@@ -768,19 +768,19 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.1089663795707747</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.3959393056621775</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.03687731364509091</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.0003819400037173182</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>5.888123746961355</v>
       </c>
     </row>
     <row r="19">
@@ -788,19 +788,19 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.1751605667767581</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.5570827906788327</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.04491459014243446</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.000369081994285807</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>6.616336478292942</v>
       </c>
     </row>
     <row r="20">
@@ -808,19 +808,19 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.268788747168146</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.8895342294545844</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.07121052810689435</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.0003691820055246353</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>7.218610920459032</v>
       </c>
     </row>
     <row r="21">
@@ -828,19 +828,19 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.3857604240824003</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.167485931086121</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.1048400916461833</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.0003502599964849651</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>8.051369171142579</v>
       </c>
     </row>
   </sheetData>

--- a/workspace/framework_paper/fp/gradient_fp_eval_times.xlsx
+++ b/workspace/framework_paper/fp/gradient_fp_eval_times.xlsx
@@ -448,19 +448,19 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0007893919968046248</v>
+        <v>0.001413777489215136</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0006229959963820875</v>
+        <v>0.001248221597634256</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008899160078726709</v>
+        <v>0.001710138238267973</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000296412002062425</v>
+        <v>0.0007148866372881457</v>
       </c>
       <c r="F2" t="n">
-        <v>2.193019996732473</v>
+        <v>2.803020060956478</v>
       </c>
     </row>
     <row r="3">
@@ -468,19 +468,19 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0008400840067770332</v>
+        <v>0.001373968267580494</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0006830139993689954</v>
+        <v>0.00123238914005924</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009924079955089837</v>
+        <v>0.001705298374872655</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000331159996567294</v>
+        <v>0.0006427092012017965</v>
       </c>
       <c r="F3" t="n">
-        <v>2.275343377739191</v>
+        <v>2.820337651073933</v>
       </c>
     </row>
     <row r="4">
@@ -488,19 +488,19 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0007881999947130681</v>
+        <v>0.001447882417123765</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0006662339984904974</v>
+        <v>0.001352224949514493</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009793319995515049</v>
+        <v>0.001806899911025539</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003401659987866879</v>
+        <v>0.0005995707743568346</v>
       </c>
       <c r="F4" t="n">
-        <v>2.391024669408798</v>
+        <v>2.987753646224737</v>
       </c>
     </row>
     <row r="5">
@@ -508,19 +508,19 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0008843100012745709</v>
+        <v>0.00153689750470221</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0007104880036786199</v>
+        <v>0.001380711700767279</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001003630006453022</v>
+        <v>0.001981522452551872</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000338423999492079</v>
+        <v>0.0007882616756251082</v>
       </c>
       <c r="F5" t="n">
-        <v>2.479341176003218</v>
+        <v>3.111202481240034</v>
       </c>
     </row>
     <row r="6">
@@ -528,19 +528,19 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0008535460056737066</v>
+        <v>0.001515016602352261</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0006986679986584932</v>
+        <v>0.001408079973771237</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0009932979987934232</v>
+        <v>0.001937737480038777</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003352339996490627</v>
+        <v>0.0006115041533485055</v>
       </c>
       <c r="F6" t="n">
-        <v>2.468851282894611</v>
+        <v>3.186009917408228</v>
       </c>
     </row>
     <row r="7">
@@ -548,19 +548,19 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0008797379978932441</v>
+        <v>0.001618054184364155</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007441119966097176</v>
+        <v>0.001495189157431014</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00106908198678866</v>
+        <v>0.002034439947456121</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0003569219983182848</v>
+        <v>0.0008357342390809208</v>
       </c>
       <c r="F7" t="n">
-        <v>2.635712263733148</v>
+        <v>3.433950301259756</v>
       </c>
     </row>
     <row r="8">
@@ -568,19 +568,19 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0009212179912719876</v>
+        <v>0.001703794156201184</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0007944499934092165</v>
+        <v>0.001481279251165688</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00110066200606525</v>
+        <v>0.002172171670245007</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003760340018197894</v>
+        <v>0.0007085426151752472</v>
       </c>
       <c r="F8" t="n">
-        <v>2.701351160407066</v>
+        <v>3.449571636468172</v>
       </c>
     </row>
     <row r="9">
@@ -588,19 +588,19 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0009319500008132309</v>
+        <v>0.001685048204381019</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0007891400007065386</v>
+        <v>0.001607514187926427</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001144340011524036</v>
+        <v>0.002136508282274008</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0003807940008118749</v>
+        <v>0.0005970175773836673</v>
       </c>
       <c r="F9" t="n">
-        <v>2.782697332799435</v>
+        <v>3.541561101078987</v>
       </c>
     </row>
     <row r="10">
@@ -608,19 +608,19 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0009932599868625403</v>
+        <v>0.00173310502897948</v>
       </c>
       <c r="C10" t="n">
-        <v>0.000824383997824043</v>
+        <v>0.001608933351235464</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001171486008679494</v>
+        <v>0.002080455797258764</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0004017680045217275</v>
+        <v>0.0006557850271929056</v>
       </c>
       <c r="F10" t="n">
-        <v>2.90157602712512</v>
+        <v>3.664311307370663</v>
       </c>
     </row>
     <row r="11">
@@ -628,19 +628,19 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.001332722010556608</v>
+        <v>0.002673905896954239</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001515297988662496</v>
+        <v>0.002425237527349964</v>
       </c>
       <c r="D11" t="n">
-        <v>0.003017974039539695</v>
+        <v>0.004512070778291672</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0003867339994758367</v>
+        <v>0.0006175391474971547</v>
       </c>
       <c r="F11" t="n">
-        <v>2.968516656160355</v>
+        <v>3.760652349144221</v>
       </c>
     </row>
     <row r="12">
@@ -648,19 +648,19 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001969517994439229</v>
+        <v>0.003538795851636678</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00292254195548594</v>
+        <v>0.003872359180240892</v>
       </c>
       <c r="D12" t="n">
-        <v>0.003310091966995969</v>
+        <v>0.004392845036927611</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0004288360057398677</v>
+        <v>0.0005567099805921316</v>
       </c>
       <c r="F12" t="n">
-        <v>3.201081767827272</v>
+        <v>3.99679329380393</v>
       </c>
     </row>
     <row r="13">
@@ -668,19 +668,19 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.003633842011913657</v>
+        <v>0.006770376580534503</v>
       </c>
       <c r="C13" t="n">
-        <v>0.006339989937841893</v>
+        <v>0.008250817622756585</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0027825000253506</v>
+        <v>0.004082048421259969</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0004011200042441487</v>
+        <v>0.0006890892185037956</v>
       </c>
       <c r="F13" t="n">
-        <v>3.409722273796797</v>
+        <v>4.327445442378521</v>
       </c>
     </row>
     <row r="14">
@@ -688,19 +688,19 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0.005230469992384314</v>
+        <v>0.009630310017964803</v>
       </c>
       <c r="C14" t="n">
-        <v>0.009772487917216495</v>
+        <v>0.01281959409883712</v>
       </c>
       <c r="D14" t="n">
-        <v>0.008139245908241719</v>
+        <v>0.009498720722040161</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0004070640017744154</v>
+        <v>0.0004980457987403497</v>
       </c>
       <c r="F14" t="n">
-        <v>3.697639360427857</v>
+        <v>4.719483923316002</v>
       </c>
     </row>
     <row r="15">
@@ -708,19 +708,19 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0.009944973828969523</v>
+        <v>0.01977909972774796</v>
       </c>
       <c r="C15" t="n">
-        <v>0.03879417071584612</v>
+        <v>0.04857965365285054</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01291843803133816</v>
+        <v>0.01611670651473105</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0004055099980905652</v>
+        <v>0.0005625466769561172</v>
       </c>
       <c r="F15" t="n">
-        <v>4.261405312269926</v>
+        <v>5.435090338140726</v>
       </c>
     </row>
     <row r="16">
@@ -728,19 +728,19 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0.02976611061953008</v>
+        <v>0.05447343833744526</v>
       </c>
       <c r="C16" t="n">
-        <v>0.09482922577881255</v>
+        <v>0.1120722926978488</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01550610190955922</v>
+        <v>0.0194647990190424</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0003790280048269779</v>
+        <v>0.0004869667562888935</v>
       </c>
       <c r="F16" t="n">
-        <v>4.747784471660853</v>
+        <v>6.018126690685749</v>
       </c>
     </row>
     <row r="17">
@@ -748,19 +748,19 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0.06512665909598582</v>
+        <v>0.1097581230464857</v>
       </c>
       <c r="C17" t="n">
-        <v>0.211364009026438</v>
+        <v>0.2500932800670853</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02088046004297212</v>
+        <v>0.02480743976542726</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0004187360010109842</v>
+        <v>0.0004713017208268866</v>
       </c>
       <c r="F17" t="n">
-        <v>5.363029298633337</v>
+        <v>6.911015069782734</v>
       </c>
     </row>
     <row r="18">
@@ -768,19 +768,19 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1089663795707747</v>
+        <v>0.1984118271875195</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3959393056621775</v>
+        <v>0.4611711517360527</v>
       </c>
       <c r="D18" t="n">
-        <v>0.03687731364509091</v>
+        <v>0.04527668676455505</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0003819400037173182</v>
+        <v>0.0003574774583103135</v>
       </c>
       <c r="F18" t="n">
-        <v>5.888123746961355</v>
+        <v>7.764483018517494</v>
       </c>
     </row>
     <row r="19">
@@ -788,19 +788,19 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1751605667767581</v>
+        <v>0.3122263127053156</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5570827906788327</v>
+        <v>0.6649956467957235</v>
       </c>
       <c r="D19" t="n">
-        <v>0.04491459014243446</v>
+        <v>0.0579281536443159</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000369081994285807</v>
+        <v>0.0003677040804177523</v>
       </c>
       <c r="F19" t="n">
-        <v>6.616336478292942</v>
+        <v>8.83447860777378</v>
       </c>
     </row>
     <row r="20">
@@ -808,19 +808,19 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0.268788747168146</v>
+        <v>0.455866144800093</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8895342294545844</v>
+        <v>1.052560932296328</v>
       </c>
       <c r="D20" t="n">
-        <v>0.07121052810689435</v>
+        <v>0.08134783892426639</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0003691820055246353</v>
+        <v>0.0004389216570416466</v>
       </c>
       <c r="F20" t="n">
-        <v>7.218610920459032</v>
+        <v>9.776215092837811</v>
       </c>
     </row>
     <row r="21">
@@ -828,19 +828,19 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0.3857604240824003</v>
+        <v>0.6984298436506652</v>
       </c>
       <c r="C21" t="n">
-        <v>1.167485931086121</v>
+        <v>1.402622971304227</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1048400916461833</v>
+        <v>0.1270808809506707</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0003502599964849651</v>
+        <v>0.0004125407198444009</v>
       </c>
       <c r="F21" t="n">
-        <v>8.051369171142579</v>
+        <v>11.00750870227814</v>
       </c>
     </row>
   </sheetData>
